--- a/Sedes_a_priorizar_Juan_Tama_2.xlsx
+++ b/Sedes_a_priorizar_Juan_Tama_2.xlsx
@@ -450,11 +450,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>219355000046</v>
+        <v>219355001051</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA LOMA ALTA</t>
+          <t>ESCUELA RURAL MIXTA EL GUADUAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -464,7 +464,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAN ANDRÉS</t>
+          <t>YAQUIVA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>51.30300603448276</v>
+        <v>61.20963681034483</v>
       </c>
     </row>
     <row r="3">
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>62.75132797413794</v>
+        <v>62.74220512931035</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>219355000143</v>
+        <v>219355800000</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA EL PICACHO</t>
+          <t>ESCUELA RURAL MIXTA ÜUS DXI`CAMINO DE SABIDURIA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -520,25 +520,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SAN ANDRÉS</t>
+          <t>YAQUIVA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>IZA</t>
+          <t>INZA</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>63.55477991379311</v>
+        <v>65.77632137931035</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>219355001361</v>
+        <v>219355000313</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>E.R.M. PIIYA THE WE´SX UUS YAT</t>
+          <t>ESCUELA RURAL MIXTA CHICHUCUE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SAN ANTONIO DE PEDREGAL</t>
+          <t>YAQUIVA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -557,16 +557,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>64.52850612068966</v>
+        <v>66.63557491379311</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>219355800000</v>
+        <v>219355000232</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA ÜUS DXI`CAMINO DE SABIDURIA</t>
+          <t>ESCUELA RURAL MIXTA  BELENCITO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>YAQUIVA</t>
+          <t>LA GAITANA JUAN TAMA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>65.78544422413793</v>
+        <v>68.39226387931035</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>219355000313</v>
+        <v>419355000223</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA CHICHUCUE</t>
+          <t>ESCUELA RURAL MIXTA YAQUIVA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -613,16 +613,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>66.64469775862069</v>
+        <v>72.09930366379309</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>419355000223</v>
+        <v>219355000283</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA YAQUIVA</t>
+          <t>ESCUELA RURAL MIXTA LA MILAGROSA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>72.10842650862068</v>
+        <v>72.40406581896552</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>219355000283</v>
+        <v>219355000321</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA LA MILAGROSA</t>
+          <t>ESCUELA RURAL MIXTA COSCURO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -669,16 +669,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>72.41318866379311</v>
+        <v>73.65553206896553</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>219355000321</v>
+        <v>219355000976</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ESCUELA RURAL MIXTA COSCURO</t>
+          <t>ESCUELA RURAL MIXTA DOS QUEBRADAS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>73.6646549137931</v>
+        <v>73.67856456896553</v>
       </c>
     </row>
   </sheetData>
